--- a/energy-fuel-type/energy-fuel-type.xlsx
+++ b/energy-fuel-type/energy-fuel-type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FDE156-AA52-4D73-A272-688CF787A814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF88AD-E5A7-403F-B345-9FF9EB569FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -105,9 +105,6 @@
     <t>owl:deprecated^^xsd:boolean</t>
   </si>
   <si>
-    <t>dcterms:replacedBy</t>
-  </si>
-  <si>
     <t>http://data.europa.eu/r5r/applicableLegislation</t>
   </si>
   <si>
@@ -219,13 +216,22 @@
     <t>Regulation (EU) 2023/1804 of the European Parliament and of the Council of 13 September 2023 on the deployment of alternative fuels infrastructure, and repealing Directive 2014/94/EU</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>Energy Fuel Type</t>
   </si>
   <si>
     <t>1.0.0</t>
+  </si>
+  <si>
+    <t>Darko Ilić (ASTRA)</t>
+  </si>
+  <si>
+    <t>Hilde Austlid (Norwegian Public Roads Administration, Statens vegvesen)</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t>dcterms:isReplacedBy</t>
   </si>
 </sst>
 </file>
@@ -630,45 +636,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6E9CF-7EDF-4777-B707-6107C91710E5}">
-  <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="98.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="98.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="77" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="51.140625" customWidth="1"/>
-    <col min="5" max="5" width="92.42578125" customWidth="1"/>
-    <col min="6" max="6" width="75.5703125" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" customWidth="1"/>
+    <col min="4" max="4" width="51.109375" customWidth="1"/>
+    <col min="5" max="5" width="92.44140625" customWidth="1"/>
+    <col min="6" max="6" width="75.5546875" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="81.85546875" customWidth="1"/>
-    <col min="9" max="9" width="58.42578125" customWidth="1"/>
+    <col min="8" max="8" width="81.88671875" customWidth="1"/>
+    <col min="9" max="9" width="58.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -676,7 +682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -684,7 +690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -692,439 +698,458 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B10)</f>
+      <c r="B13" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B12)</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/1.0.0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="str">
-        <f t="shared" ref="A19" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B19,"/","-"))," ","-"),",",""))</f>
+    </row>
+    <row r="21" spans="1:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="str">
+        <f t="shared" ref="A21" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B21,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="10" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A20:A23)</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-ac, https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-dc, https://w3id.org/mobilitydcat-ap/energy-fuel-type/hydrogen, https://w3id.org/mobilitydcat-ap/energy-fuel-type/ammonia</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="H19" s="1"/>
-      <c r="I19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="str">
-        <f t="shared" ref="A20:A21" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B20,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-ac</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10" t="str">
-        <f>A19</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-dc</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>32</v>
+      <c r="B21" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="12"/>
-      <c r="E21" s="10"/>
+      <c r="E21" s="10" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A22:A25)</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-ac, https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-dc, https://w3id.org/mobilitydcat-ap/energy-fuel-type/hydrogen, https://w3id.org/mobilitydcat-ap/energy-fuel-type/ammonia</v>
+      </c>
       <c r="F21" s="10"/>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="str">
+        <f t="shared" ref="A22:A23" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B22,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-ac</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="str">
-        <f t="shared" ref="A22:A34" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B22,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/hydrogen</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="12"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10" t="str">
-        <f>A19</f>
+        <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/ammonia</v>
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/electricity-dc</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="12"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10" t="str">
-        <f>A19</f>
+        <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>35</v>
+        <f t="shared" ref="A24:A36" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B24,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/hydrogen</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="12"/>
-      <c r="E24" s="10" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A25:A29)</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biomass-fuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/biofuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/biogas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-synthetic-fuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-ammonia</v>
-      </c>
-      <c r="F24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biomass-fuel</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/ammonia</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="12"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10" t="str">
-        <f>A24</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/zero-emission-energy-types</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biofuel</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="10" t="str">
-        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
       </c>
+      <c r="B26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="10" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A27:A31)</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biomass-fuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/biofuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/biogas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-synthetic-fuel, https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-ammonia</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="H26" s="1"/>
       <c r="I26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biogas</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biomass-fuel</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>38</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="10"/>
       <c r="F27" s="10" t="str">
-        <f>A24</f>
+        <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
       </c>
+      <c r="H27" s="1"/>
       <c r="I27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-synthetic-fuel</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biofuel</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F28" s="10" t="str">
-        <f>A24</f>
+        <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-ammonia</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/biogas</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F29" s="10" t="str">
-        <f>A24</f>
+        <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A31:A34)</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/compressed-natural-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-natural-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-petroleum-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/non-renewable-synthetic-fuel</v>
-      </c>
-      <c r="F30" s="10"/>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-synthetic-fuel</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="10" t="str">
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
+      </c>
       <c r="I30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/compressed-natural-gas</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-ammonia</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F31" s="10" t="str">
-        <f>A30</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/renewable-fuels</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-natural-gas</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="10" t="str">
-        <f>A30</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
       </c>
+      <c r="B32" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A33:A36)</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/compressed-natural-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-natural-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-petroleum-gas, https://w3id.org/mobilitydcat-ap/energy-fuel-type/non-renewable-synthetic-fuel</v>
+      </c>
+      <c r="F32" s="10"/>
       <c r="I32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-petroleum-gas</v>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/compressed-natural-gas</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F33" s="10" t="str">
-        <f>A30</f>
+        <f>A32</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="str">
         <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-natural-gas</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="10" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
+      </c>
+      <c r="I34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/liquefied-petroleum-gas</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="10" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
+      </c>
+      <c r="I35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="str">
+        <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non-renewable-synthetic-fuel</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="10" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
+      </c>
+      <c r="I36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="str">
+        <f t="shared" ref="A37:A38" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B37,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/fossil-fuels</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F34" s="10" t="str">
-        <f>A30</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/non‑renewable-alternative-and-transitional-fossil-fuels</v>
-      </c>
-      <c r="I34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="str">
-        <f t="shared" ref="A35:A36" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B35,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/fossil-fuels</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A36:A37)</f>
+      <c r="E37" s="1" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A38:A39)</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/petrol, https://w3id.org/mobilitydcat-ap/energy-fuel-type/diesel</v>
       </c>
-      <c r="F35" s="10"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="str">
+      <c r="F37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="str">
         <f t="shared" si="3"/>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/petrol</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="10" t="str">
+        <f>A37</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/fossil-fuels</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="str">
+        <f t="shared" ref="A39" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B39,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/diesel</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="10" t="str">
-        <f>A35</f>
+      <c r="F39" s="10" t="str">
+        <f>A37</f>
         <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/fossil-fuels</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="str">
-        <f t="shared" ref="A37" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B37,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/diesel</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="10" t="str">
-        <f>A35</f>
-        <v>https://w3id.org/mobilitydcat-ap/energy-fuel-type/fossil-fuels</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F44" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{88DD0E19-390C-4E8C-B1D4-C8022AB762F5}"/>
-    <hyperlink ref="I18" r:id="rId2" xr:uid="{CB0B5D26-657C-45EC-A00A-F5FDA39D71A1}"/>
+    <hyperlink ref="B15" r:id="rId1" xr:uid="{88DD0E19-390C-4E8C-B1D4-C8022AB762F5}"/>
+    <hyperlink ref="I20" r:id="rId2" xr:uid="{CB0B5D26-657C-45EC-A00A-F5FDA39D71A1}"/>
     <hyperlink ref="B1" r:id="rId3" xr:uid="{7A5E5744-6303-4F65-A6C1-F3AA593679B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1134,82 +1159,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.85546875" customWidth="1"/>
-    <col min="2" max="2" width="52.42578125" customWidth="1"/>
-    <col min="3" max="3" width="47.140625" customWidth="1"/>
-    <col min="4" max="4" width="51.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.88671875" customWidth="1"/>
+    <col min="2" max="2" width="52.44140625" customWidth="1"/>
+    <col min="3" max="3" width="47.109375" customWidth="1"/>
+    <col min="4" max="4" width="51.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
     </row>
@@ -1424,6 +1449,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
@@ -1432,15 +1466,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1463,6 +1488,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F704F36C-6F34-42D8-A9E1-097741891E9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1471,12 +1504,4 @@
     <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>